--- a/astro-site/public/dl/coffee-shop-checklist-templates/06-coffee-shop-event-checklists.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/06-coffee-shop-event-checklists.xlsx
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Offer mimosas/bellinis as an add-on (only with an alcohol license; 21+ with ID)</t>
+          <t>Offer mimosas/bellinis as an add-on (only with an alcohol license; guests 21+ with ID, served only by staff old enough under your state's law)</t>
         </is>
       </c>
       <c r="C23" s="29" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B16" s="36" t="inlineStr">
         <is>
-          <t>Welcome drink for couples: alcohol-free, or a mimosa only where your license and state allow giving alcohol away (21+ with ID)</t>
+          <t>Welcome drink for couples: alcohol-free, or a mimosa only where your license and state allow giving alcohol away, served by staff old enough under your state's law (21+ with ID)</t>
         </is>
       </c>
       <c r="C16" s="29" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>2 weeks out</t>
         </is>
       </c>
       <c r="F6" s="30" t="n"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>2 weeks out</t>
         </is>
       </c>
       <c r="F8" s="30" t="n"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Special holiday coffee: gingerbread latte, pumpkin spice</t>
+          <t>Special holiday coffee: gingerbread latte, peppermint mocha, eggnog latte</t>
         </is>
       </c>
       <c r="C15" s="29" t="inlineStr">
@@ -2521,9 +2521,9 @@
       <c r="A21" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>Check stock for the week with no deliveries</t>
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Check stock for the holiday weeks: confirm your suppliers' delivery days around Dec 25 and Jan 1</t>
         </is>
       </c>
       <c r="C21" s="29" t="inlineStr">
